--- a/GourmetProject/GameConfig/Datas/boss.xlsx
+++ b/GourmetProject/GameConfig/Datas/boss.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,74 +466,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>##comment</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Boss ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Boss名称</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>角色池ID</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>解锁条件</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>随机权重</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>所属周数</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>分数曲线ID</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>关卡修饰符</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>boss_glutton</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>大胃王挑战</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>limit_serve</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -541,18 +561,18 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>boss_iron</t>
+          <t>boss_glutton</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>铁胃霸主</t>
+          <t>大胃王挑战</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -560,7 +580,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>small_board</t>
+          <t>limit_serve</t>
         </is>
       </c>
     </row>
@@ -568,24 +588,51 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>boss_final</t>
+          <t>boss_iron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>终极美食家</t>
+          <t>铁胃霸主</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
+        <is>
+          <t>small_board</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>boss_final</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>终极美食家</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>small_board</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/boss.xlsx
+++ b/GourmetProject/GameConfig/Datas/boss.xlsx
@@ -471,42 +471,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Boss ID</t>
+          <t>Boss配置ID。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boss名称</t>
+          <t>Boss显示名称。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>角色池ID</t>
+          <t>Boss自身角色池，空=任意角色；逗号分隔 character.id。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>解锁条件</t>
+          <t>解锁条件，空=默认解锁。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>随机权重</t>
+          <t>同一候选池内按该权重随机。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>所属周数</t>
+          <t>限定周序号；0=任意Boss周。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>分数曲线ID</t>
+          <t>Boss目标分曲线；空=使用当前周目标分曲线。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>关卡修饰符</t>
+          <t>Boss特殊机制标识。</t>
         </is>
       </c>
     </row>
